--- a/Data.xlsx
+++ b/Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\Year 2\TesselationTesting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E319B85E-D70A-41F1-BFFD-BDBEEB22E5C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8052E586-CB76-4724-8844-F2333159CD0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Test 1</t>
   </si>
@@ -50,9 +50,6 @@
     <t>Average (FPS)</t>
   </si>
   <si>
-    <t>No tessellation</t>
-  </si>
-  <si>
     <t>Tessellation factor 4</t>
   </si>
   <si>
@@ -102,6 +99,15 @@
   </si>
   <si>
     <t>10x10 City; Seed 2; Min 3 Height; Max 5 Height</t>
+  </si>
+  <si>
+    <t>Tessellation factor 1 (no tesselation)</t>
+  </si>
+  <si>
+    <t>Triangle Count</t>
+  </si>
+  <si>
+    <t>Vertex Count</t>
   </si>
 </sst>
 </file>
@@ -143,9 +149,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -426,16 +433,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.33203125" customWidth="1"/>
+    <col min="1" max="1" width="39.44140625" customWidth="1"/>
     <col min="5" max="5" width="12.77734375" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -449,10 +458,16 @@
       <c r="E1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="B2">
         <v>99.74</v>
@@ -467,10 +482,16 @@
         <f>AVERAGE(B2:D2)</f>
         <v>99.236666666666665</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G2" s="2">
+        <v>5183814</v>
+      </c>
+      <c r="H2" s="2">
+        <v>8321936</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>95.07</v>
@@ -485,10 +506,16 @@
         <f t="shared" ref="E3:E18" si="0">AVERAGE(B3:D3)</f>
         <v>94.11</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G3" s="2">
+        <v>5183814</v>
+      </c>
+      <c r="H3" s="2">
+        <v>8321936</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4">
         <v>94.57</v>
@@ -503,10 +530,16 @@
         <f t="shared" si="0"/>
         <v>93.686666666666667</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G4" s="2">
+        <v>5183814</v>
+      </c>
+      <c r="H4" s="2">
+        <v>8321936</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5">
         <v>90.85</v>
@@ -521,10 +554,16 @@
         <f t="shared" si="0"/>
         <v>90.95</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G5" s="2">
+        <v>5183814</v>
+      </c>
+      <c r="H5" s="2">
+        <v>8321936</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6">
         <v>91.52</v>
@@ -539,113 +578,191 @@
         <f t="shared" si="0"/>
         <v>90.726666666666674</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G6" s="2">
+        <v>5183814</v>
+      </c>
+      <c r="H6" s="2">
+        <v>8321936</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G7" s="2">
+        <v>5183814</v>
+      </c>
+      <c r="H7" s="2">
+        <v>8321936</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="1" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="E8" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G8" s="2">
+        <v>5183814</v>
+      </c>
+      <c r="H8" s="2">
+        <v>8321936</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="1" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="E9" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G9" s="2">
+        <v>5183814</v>
+      </c>
+      <c r="H9" s="2">
+        <v>8321936</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="1" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="E10" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G10" s="2">
+        <v>5183814</v>
+      </c>
+      <c r="H10" s="2">
+        <v>8321936</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="1" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="E11" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G11" s="2">
+        <v>5183814</v>
+      </c>
+      <c r="H11" s="2">
+        <v>8321936</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="1" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="E12" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G12" s="2">
+        <v>5183814</v>
+      </c>
+      <c r="H12" s="2">
+        <v>8321936</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="1" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="E13" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G13" s="2">
+        <v>5183814</v>
+      </c>
+      <c r="H13" s="2">
+        <v>8321936</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="1" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="E14" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G14" s="2">
+        <v>5183814</v>
+      </c>
+      <c r="H14" s="2">
+        <v>8321936</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="1" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="E15" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G15" s="2">
+        <v>5183814</v>
+      </c>
+      <c r="H15" s="2">
+        <v>8321936</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="1" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="E16" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G16" s="2">
+        <v>5183814</v>
+      </c>
+      <c r="H16" s="2">
+        <v>8321936</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="1" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="E17" s="1" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G17" s="2">
+        <v>5183814</v>
+      </c>
+      <c r="H17" s="2">
+        <v>8321936</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="1" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>20</v>
-      </c>
       <c r="E18" s="1" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
+      </c>
+      <c r="G18" s="2">
+        <v>5183814</v>
+      </c>
+      <c r="H18" s="2">
+        <v>8321936</v>
       </c>
     </row>
   </sheetData>

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -8,13 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\Year 2\TesselationTesting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8052E586-CB76-4724-8844-F2333159CD0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0CFD78D-3801-49D5-B665-578D9141E506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$A$2:$A$18</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$E$2:$E$18</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$J$2</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$M$6</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$M$6</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Test 1</t>
   </si>
@@ -47,67 +54,19 @@
     <t>Test 3</t>
   </si>
   <si>
-    <t>Average (FPS)</t>
-  </si>
-  <si>
-    <t>Tessellation factor 4</t>
-  </si>
-  <si>
-    <t>Tessellation factor 8</t>
-  </si>
-  <si>
-    <t>Tessellation factor 12</t>
-  </si>
-  <si>
-    <t>Tessellation factor 16</t>
-  </si>
-  <si>
-    <t>Tessellation factor 20</t>
-  </si>
-  <si>
-    <t>Tessellation factor 24</t>
-  </si>
-  <si>
-    <t>Tessellationfactor 28</t>
-  </si>
-  <si>
-    <t>Tessellation factor 32</t>
-  </si>
-  <si>
-    <t>Tessellation factor 36</t>
-  </si>
-  <si>
-    <t>Tessellation factor 40</t>
-  </si>
-  <si>
-    <t>Tessellation factor 44</t>
-  </si>
-  <si>
-    <t>Tessellation factor 48</t>
-  </si>
-  <si>
-    <t>Tessellation factor 52</t>
-  </si>
-  <si>
-    <t>Tessellation factor 56</t>
-  </si>
-  <si>
-    <t>Tessellation factor 60</t>
-  </si>
-  <si>
-    <t>Tessellationfactor 64</t>
-  </si>
-  <si>
     <t>10x10 City; Seed 2; Min 3 Height; Max 5 Height</t>
-  </si>
-  <si>
-    <t>Tessellation factor 1 (no tesselation)</t>
   </si>
   <si>
     <t>Triangle Count</t>
   </si>
   <si>
     <t>Vertex Count</t>
+  </si>
+  <si>
+    <t>Tessellation factor</t>
+  </si>
+  <si>
+    <t>Average FPS</t>
   </si>
 </sst>
 </file>
@@ -149,10 +108,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -168,6 +128,1117 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>FPS across tessellatio</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t>n factors</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.2597845581802275"/>
+          <c:y val="0"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>FPS</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$18</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>64</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$E$2:$E$18</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="17"/>
+                <c:pt idx="0">
+                  <c:v>99.236666666666665</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>94.11</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>93.686666666666667</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>90.95</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>90.726666666666674</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>90.613333333333344</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>89.17</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>87.12</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>85.490000000000009</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>83.306666666666672</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>81.583333333333329</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>80.25</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>78.486666666666665</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>76.516666666666666</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>74.796666666666667</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>73.073333333333323</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>71.463333333333338</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-77AC-4262-BA97-365C23CC0218}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="316393616"/>
+        <c:axId val="316395056"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="316393616"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Tessellation factor</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="316395056"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="316395056"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Average FPS</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="316393616"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>312420</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87DCC73D-A7D5-4D22-1163-AD721A04576F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -433,18 +1504,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="39.44140625" customWidth="1"/>
+    <col min="1" max="1" width="18.109375" customWidth="1"/>
     <col min="5" max="5" width="12.77734375" customWidth="1"/>
     <col min="7" max="7" width="15.88671875" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -456,18 +1527,21 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H1" t="s">
-        <v>23</v>
-      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>21</v>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <v>1</v>
       </c>
       <c r="B2">
         <v>99.74</v>
@@ -489,8 +1563,8 @@
         <v>8321936</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <v>4</v>
       </c>
       <c r="B3">
@@ -513,9 +1587,9 @@
         <v>8321936</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>5</v>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>8</v>
       </c>
       <c r="B4">
         <v>94.57</v>
@@ -537,9 +1611,9 @@
         <v>8321936</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>6</v>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>12</v>
       </c>
       <c r="B5">
         <v>90.85</v>
@@ -561,9 +1635,9 @@
         <v>8321936</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>7</v>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <v>16</v>
       </c>
       <c r="B6">
         <v>91.52</v>
@@ -585,13 +1659,22 @@
         <v>8321936</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="1" t="e">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <v>20</v>
+      </c>
+      <c r="B7">
+        <v>90.97</v>
+      </c>
+      <c r="C7">
+        <v>89.93</v>
+      </c>
+      <c r="D7">
+        <v>90.94</v>
+      </c>
+      <c r="E7" s="1">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>90.613333333333344</v>
       </c>
       <c r="G7" s="2">
         <v>5183814</v>
@@ -600,13 +1683,22 @@
         <v>8321936</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="1" t="e">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>24</v>
+      </c>
+      <c r="B8">
+        <v>89.56</v>
+      </c>
+      <c r="C8">
+        <v>89.16</v>
+      </c>
+      <c r="D8">
+        <v>88.79</v>
+      </c>
+      <c r="E8" s="1">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>89.17</v>
       </c>
       <c r="G8" s="2">
         <v>5183814</v>
@@ -615,13 +1707,22 @@
         <v>8321936</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="1" t="e">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <v>28</v>
+      </c>
+      <c r="B9">
+        <v>87.2</v>
+      </c>
+      <c r="C9">
+        <v>87.08</v>
+      </c>
+      <c r="D9">
+        <v>87.08</v>
+      </c>
+      <c r="E9" s="1">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>87.12</v>
       </c>
       <c r="G9" s="2">
         <v>5183814</v>
@@ -630,13 +1731,22 @@
         <v>8321936</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="1" t="e">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <v>32</v>
+      </c>
+      <c r="B10">
+        <v>85.65</v>
+      </c>
+      <c r="C10">
+        <v>85.33</v>
+      </c>
+      <c r="D10">
+        <v>85.49</v>
+      </c>
+      <c r="E10" s="1">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>85.490000000000009</v>
       </c>
       <c r="G10" s="2">
         <v>5183814</v>
@@ -645,13 +1755,22 @@
         <v>8321936</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="1" t="e">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <v>36</v>
+      </c>
+      <c r="B11">
+        <v>83.69</v>
+      </c>
+      <c r="C11">
+        <v>83.34</v>
+      </c>
+      <c r="D11">
+        <v>82.89</v>
+      </c>
+      <c r="E11" s="1">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>83.306666666666672</v>
       </c>
       <c r="G11" s="2">
         <v>5183814</v>
@@ -660,13 +1779,22 @@
         <v>8321936</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="1" t="e">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <v>40</v>
+      </c>
+      <c r="B12">
+        <v>81.59</v>
+      </c>
+      <c r="C12">
+        <v>81.459999999999994</v>
+      </c>
+      <c r="D12">
+        <v>81.7</v>
+      </c>
+      <c r="E12" s="1">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>81.583333333333329</v>
       </c>
       <c r="G12" s="2">
         <v>5183814</v>
@@ -675,13 +1803,22 @@
         <v>8321936</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="1" t="e">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <v>44</v>
+      </c>
+      <c r="B13">
+        <v>80.37</v>
+      </c>
+      <c r="C13">
+        <v>80.25</v>
+      </c>
+      <c r="D13">
+        <v>80.13</v>
+      </c>
+      <c r="E13" s="1">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>80.25</v>
       </c>
       <c r="G13" s="2">
         <v>5183814</v>
@@ -690,13 +1827,22 @@
         <v>8321936</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" s="1" t="e">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <v>48</v>
+      </c>
+      <c r="B14">
+        <v>78.849999999999994</v>
+      </c>
+      <c r="C14">
+        <v>78.430000000000007</v>
+      </c>
+      <c r="D14">
+        <v>78.180000000000007</v>
+      </c>
+      <c r="E14" s="1">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>78.486666666666665</v>
       </c>
       <c r="G14" s="2">
         <v>5183814</v>
@@ -705,13 +1851,22 @@
         <v>8321936</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" s="1" t="e">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <v>52</v>
+      </c>
+      <c r="B15">
+        <v>76.599999999999994</v>
+      </c>
+      <c r="C15">
+        <v>76.5</v>
+      </c>
+      <c r="D15">
+        <v>76.45</v>
+      </c>
+      <c r="E15" s="1">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>76.516666666666666</v>
       </c>
       <c r="G15" s="2">
         <v>5183814</v>
@@ -720,13 +1875,22 @@
         <v>8321936</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="1" t="e">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <v>56</v>
+      </c>
+      <c r="B16">
+        <v>74.930000000000007</v>
+      </c>
+      <c r="C16">
+        <v>74.760000000000005</v>
+      </c>
+      <c r="D16">
+        <v>74.7</v>
+      </c>
+      <c r="E16" s="1">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>74.796666666666667</v>
       </c>
       <c r="G16" s="2">
         <v>5183814</v>
@@ -736,12 +1900,21 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" s="1" t="e">
+      <c r="A17" s="3">
+        <v>60</v>
+      </c>
+      <c r="B17">
+        <v>73.239999999999995</v>
+      </c>
+      <c r="C17">
+        <v>73.02</v>
+      </c>
+      <c r="D17">
+        <v>72.959999999999994</v>
+      </c>
+      <c r="E17" s="1">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>73.073333333333323</v>
       </c>
       <c r="G17" s="2">
         <v>5183814</v>
@@ -751,12 +1924,21 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>19</v>
-      </c>
-      <c r="E18" s="1" t="e">
+      <c r="A18" s="3">
+        <v>64</v>
+      </c>
+      <c r="B18">
+        <v>71.53</v>
+      </c>
+      <c r="C18">
+        <v>71.45</v>
+      </c>
+      <c r="D18">
+        <v>71.41</v>
+      </c>
+      <c r="E18" s="1">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>71.463333333333338</v>
       </c>
       <c r="G18" s="2">
         <v>5183814</v>
@@ -768,5 +1950,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Data.xlsx
+++ b/Data.xlsx
@@ -8,20 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\Year 2\TesselationTesting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0CFD78D-3801-49D5-B665-578D9141E506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCEB62A6-0272-48EF-B6CD-20565997B099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Tessellation Factors" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$A$2:$A$18</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$E$2:$E$18</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$J$2</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$M$6</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$M$6</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -43,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="18">
   <si>
     <t>Test 1</t>
   </si>
@@ -68,11 +62,44 @@
   <si>
     <t>Average FPS</t>
   </si>
+  <si>
+    <t>Triangle Count (in millions)</t>
+  </si>
+  <si>
+    <t>Rows and Columns</t>
+  </si>
+  <si>
+    <t>15x15</t>
+  </si>
+  <si>
+    <t>3x3</t>
+  </si>
+  <si>
+    <t>6x6</t>
+  </si>
+  <si>
+    <t>9x9</t>
+  </si>
+  <si>
+    <t>12x12</t>
+  </si>
+  <si>
+    <t>18x18</t>
+  </si>
+  <si>
+    <t>21x21</t>
+  </si>
+  <si>
+    <t>crashes</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.000,,"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -108,11 +135,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -238,7 +266,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$18</c:f>
+              <c:f>'Tessellation Factors'!$A$2:$A$18</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="17"/>
@@ -298,7 +326,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$2:$E$18</c:f>
+              <c:f>'Tessellation Factors'!$E$2:$E$18</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="17"/>
@@ -644,7 +672,490 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>FPS across city sizes</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Average FPS</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet2!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.000,,</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>446196</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2557912</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6588388</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12503168</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20099300</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>29901464</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$F$2:$F$7</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>115.24666666666667</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>106.07333333333334</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>96.173333333333332</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>80.926666666666677</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>68.02</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>56.973333333333329</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-25C9-4CE3-89B2-C5FC0CC3035C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1988097360"/>
+        <c:axId val="1988095440"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1988097360"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Triangles in scene (in millions)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="#,##0.000,," sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1988095440"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1988095440"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Average</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>FPS</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1988097360"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1200,6 +1711,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -1221,6 +2248,47 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87DCC73D-A7D5-4D22-1163-AD721A04576F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>312420</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BF8B72D-AB5A-5E10-0B84-0CCDBEF3D45F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1507,7 +2575,7 @@
   <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.109375" customWidth="1"/>
+    <col min="1" max="1" width="24.5546875" customWidth="1"/>
     <col min="5" max="5" width="12.77734375" customWidth="1"/>
     <col min="7" max="7" width="15.88671875" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
@@ -1530,10 +2598,10 @@
         <v>7</v>
       </c>
       <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
         <v>4</v>
-      </c>
-      <c r="H1" t="s">
-        <v>5</v>
       </c>
       <c r="J1" t="s">
         <v>3</v>
@@ -1952,4 +3020,212 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB0519DB-39C6-4963-B577-A1DDE442233F}">
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.5546875" customWidth="1"/>
+    <col min="2" max="2" width="26.21875" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" customWidth="1"/>
+    <col min="7" max="7" width="9" customWidth="1"/>
+    <col min="8" max="8" width="17.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="4">
+        <v>446196</v>
+      </c>
+      <c r="C2">
+        <v>115.9</v>
+      </c>
+      <c r="D2">
+        <v>115.21</v>
+      </c>
+      <c r="E2">
+        <v>114.63</v>
+      </c>
+      <c r="F2" s="1">
+        <f>AVERAGE(C2:E2)</f>
+        <v>115.24666666666667</v>
+      </c>
+      <c r="H2" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="4">
+        <v>2557912</v>
+      </c>
+      <c r="C3">
+        <v>106.71</v>
+      </c>
+      <c r="D3">
+        <v>106.04</v>
+      </c>
+      <c r="E3">
+        <v>105.47</v>
+      </c>
+      <c r="F3" s="1">
+        <f t="shared" ref="F3:F8" si="0">AVERAGE(C3:E3)</f>
+        <v>106.07333333333334</v>
+      </c>
+      <c r="H3" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="4">
+        <v>6588388</v>
+      </c>
+      <c r="C4">
+        <v>96.89</v>
+      </c>
+      <c r="D4">
+        <v>96.23</v>
+      </c>
+      <c r="E4">
+        <v>95.4</v>
+      </c>
+      <c r="F4" s="1">
+        <f t="shared" si="0"/>
+        <v>96.173333333333332</v>
+      </c>
+      <c r="H4" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="4">
+        <v>12503168</v>
+      </c>
+      <c r="C5">
+        <v>80.97</v>
+      </c>
+      <c r="D5">
+        <v>81.260000000000005</v>
+      </c>
+      <c r="E5">
+        <v>80.55</v>
+      </c>
+      <c r="F5" s="1">
+        <f t="shared" si="0"/>
+        <v>80.926666666666677</v>
+      </c>
+      <c r="H5" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="4">
+        <v>20099300</v>
+      </c>
+      <c r="C6">
+        <v>67.88</v>
+      </c>
+      <c r="D6">
+        <v>68.77</v>
+      </c>
+      <c r="E6">
+        <v>67.41</v>
+      </c>
+      <c r="F6" s="1">
+        <f t="shared" si="0"/>
+        <v>68.02</v>
+      </c>
+      <c r="H6" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="4">
+        <v>29901464</v>
+      </c>
+      <c r="C7">
+        <v>58.03</v>
+      </c>
+      <c r="D7">
+        <v>56.73</v>
+      </c>
+      <c r="E7">
+        <v>56.16</v>
+      </c>
+      <c r="F7" s="1">
+        <f t="shared" si="0"/>
+        <v>56.973333333333329</v>
+      </c>
+      <c r="H7" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="4">
+        <v>40374324</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="3">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Data.xlsx
+++ b/Data.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\Year 2\TesselationTesting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCEB62A6-0272-48EF-B6CD-20565997B099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11F2A50-DB99-46AB-B7C6-B6E962345F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tessellation Factors" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Cities" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -767,7 +767,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet2!$B$2:$B$7</c:f>
+              <c:f>Cities!$B$2:$B$7</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000,,</c:formatCode>
                 <c:ptCount val="6"/>
@@ -794,7 +794,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet2!$F$2:$F$7</c:f>
+              <c:f>Cities!$F$2:$F$7</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="6"/>
@@ -3098,7 +3098,7 @@
         <v>105.47</v>
       </c>
       <c r="F3" s="1">
-        <f t="shared" ref="F3:F8" si="0">AVERAGE(C3:E3)</f>
+        <f t="shared" ref="F3:F7" si="0">AVERAGE(C3:E3)</f>
         <v>106.07333333333334</v>
       </c>
       <c r="H3" s="3">

--- a/Data.xlsx
+++ b/Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\Year 2\TesselationTesting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11F2A50-DB99-46AB-B7C6-B6E962345F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46541822-6F17-48C1-B8B2-74F02B14B451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
   <si>
     <t>Test 1</t>
   </si>
@@ -87,10 +87,7 @@
     <t>18x18</t>
   </si>
   <si>
-    <t>21x21</t>
-  </si>
-  <si>
-    <t>crashes</t>
+    <t>No tessellation</t>
   </si>
 </sst>
 </file>
@@ -706,7 +703,14 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
               <a:t>FPS across city sizes</a:t>
             </a:r>
           </a:p>
@@ -744,30 +748,135 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Average FPS</c:v>
+            <c:v>TF1</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
+          <c:invertIfNegative val="0"/>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="25400" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="2"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:cat>
             <c:numRef>
-              <c:f>Cities!$B$2:$B$7</c:f>
+              <c:f>Cities!$B$11:$B$16</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.000,,</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>446196</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2557912</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6588388</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12503168</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20099300</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>29901464</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Cities!$F$11:$F$16</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>119.69</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>109.31666666666666</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>91.446666666666673</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>79.733333333333334</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>73.056666666666672</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>65.95</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-FDA7-46A1-B02D-CDB22048C60C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>TF20</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="25400" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="2"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:cat>
+            <c:numRef>
+              <c:f>Cities!$B$11:$B$16</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.000,,</c:formatCode>
                 <c:ptCount val="6"/>
@@ -799,30 +908,29 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>115.24666666666667</c:v>
+                  <c:v>118.44333333333333</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>106.07333333333334</c:v>
+                  <c:v>104.99333333333334</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>96.173333333333332</c:v>
+                  <c:v>88.256666666666661</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>80.926666666666677</c:v>
+                  <c:v>76.59</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>68.02</c:v>
+                  <c:v>71.163333333333341</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>56.973333333333329</c:v>
+                  <c:v>65.073333333333338</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-25C9-4CE3-89B2-C5FC0CC3035C}"/>
+              <c16:uniqueId val="{00000002-FDA7-46A1-B02D-CDB22048C60C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -834,12 +942,13 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="1988097360"/>
-        <c:axId val="1988095440"/>
-      </c:lineChart>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1465790543"/>
+        <c:axId val="1465784783"/>
+      </c:barChart>
       <c:catAx>
-        <c:axId val="1988097360"/>
+        <c:axId val="1465790543"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -866,8 +975,13 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>Triangles in scene (in millions)</a:t>
+                  <a:t>Triangles</a:t>
                 </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> in scene (in millions)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -937,7 +1051,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1988095440"/>
+        <c:crossAx val="1465784783"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -945,7 +1059,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1988095440"/>
+        <c:axId val="1465784783"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -986,15 +1100,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>Average</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:t> </a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>FPS</a:t>
+                  <a:t>Average FPS</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -1059,7 +1165,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1988097360"/>
+        <c:crossAx val="1465790543"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1071,6 +1177,37 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:extLst>
@@ -1712,7 +1849,7 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -1820,11 +1957,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -1835,11 +1967,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -1871,9 +1998,6 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2272,23 +2396,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>11430</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>598713</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>312420</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>11430</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>370114</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>4354</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
+        <xdr:cNvPr id="5" name="Chart 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BF8B72D-AB5A-5E10-0B84-0CCDBEF3D45F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82796868-E333-EEE0-B037-AA9AA566D28C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3024,7 +3148,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB0519DB-39C6-4963-B577-A1DDE442233F}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.5546875" customWidth="1"/>
@@ -3065,17 +3189,17 @@
         <v>446196</v>
       </c>
       <c r="C2">
-        <v>115.9</v>
+        <v>118.85</v>
       </c>
       <c r="D2">
-        <v>115.21</v>
+        <v>118.42</v>
       </c>
       <c r="E2">
-        <v>114.63</v>
+        <v>118.06</v>
       </c>
       <c r="F2" s="1">
         <f>AVERAGE(C2:E2)</f>
-        <v>115.24666666666667</v>
+        <v>118.44333333333333</v>
       </c>
       <c r="H2" s="3">
         <v>20</v>
@@ -3089,17 +3213,17 @@
         <v>2557912</v>
       </c>
       <c r="C3">
-        <v>106.71</v>
+        <v>105.44</v>
       </c>
       <c r="D3">
-        <v>106.04</v>
+        <v>104.81</v>
       </c>
       <c r="E3">
-        <v>105.47</v>
+        <v>104.73</v>
       </c>
       <c r="F3" s="1">
         <f t="shared" ref="F3:F7" si="0">AVERAGE(C3:E3)</f>
-        <v>106.07333333333334</v>
+        <v>104.99333333333334</v>
       </c>
       <c r="H3" s="3">
         <v>20</v>
@@ -3113,17 +3237,17 @@
         <v>6588388</v>
       </c>
       <c r="C4">
-        <v>96.89</v>
+        <v>88.74</v>
       </c>
       <c r="D4">
-        <v>96.23</v>
+        <v>88.25</v>
       </c>
       <c r="E4">
-        <v>95.4</v>
+        <v>87.78</v>
       </c>
       <c r="F4" s="1">
         <f t="shared" si="0"/>
-        <v>96.173333333333332</v>
+        <v>88.256666666666661</v>
       </c>
       <c r="H4" s="3">
         <v>20</v>
@@ -3137,17 +3261,17 @@
         <v>12503168</v>
       </c>
       <c r="C5">
-        <v>80.97</v>
+        <v>76.7</v>
       </c>
       <c r="D5">
-        <v>81.260000000000005</v>
+        <v>76.66</v>
       </c>
       <c r="E5">
-        <v>80.55</v>
+        <v>76.41</v>
       </c>
       <c r="F5" s="1">
         <f t="shared" si="0"/>
-        <v>80.926666666666677</v>
+        <v>76.59</v>
       </c>
       <c r="H5" s="3">
         <v>20</v>
@@ -3161,17 +3285,17 @@
         <v>20099300</v>
       </c>
       <c r="C6">
-        <v>67.88</v>
+        <v>71.540000000000006</v>
       </c>
       <c r="D6">
-        <v>68.77</v>
+        <v>71.05</v>
       </c>
       <c r="E6">
-        <v>67.41</v>
+        <v>70.900000000000006</v>
       </c>
       <c r="F6" s="1">
         <f t="shared" si="0"/>
-        <v>68.02</v>
+        <v>71.163333333333341</v>
       </c>
       <c r="H6" s="3">
         <v>20</v>
@@ -3185,44 +3309,181 @@
         <v>29901464</v>
       </c>
       <c r="C7">
-        <v>58.03</v>
+        <v>65.95</v>
       </c>
       <c r="D7">
-        <v>56.73</v>
+        <v>65.22</v>
       </c>
       <c r="E7">
-        <v>56.16</v>
+        <v>64.05</v>
       </c>
       <c r="F7" s="1">
         <f t="shared" si="0"/>
-        <v>56.973333333333329</v>
+        <v>65.073333333333338</v>
       </c>
       <c r="H7" s="3">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="4">
-        <v>40374324</v>
-      </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="B8" s="4"/>
+      <c r="F8" s="1"/>
       <c r="H8" s="3">
         <v>20</v>
       </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="4">
+        <v>446196</v>
+      </c>
+      <c r="C11">
+        <v>120.42</v>
+      </c>
+      <c r="D11">
+        <v>119.66</v>
+      </c>
+      <c r="E11">
+        <v>118.99</v>
+      </c>
+      <c r="F11" s="1">
+        <f>AVERAGE(C11:E11)</f>
+        <v>119.69</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="4">
+        <v>2557912</v>
+      </c>
+      <c r="C12">
+        <v>109.89</v>
+      </c>
+      <c r="D12">
+        <v>109.21</v>
+      </c>
+      <c r="E12">
+        <v>108.85</v>
+      </c>
+      <c r="F12" s="1">
+        <f t="shared" ref="F12:F16" si="1">AVERAGE(C12:E12)</f>
+        <v>109.31666666666666</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="4">
+        <v>6588388</v>
+      </c>
+      <c r="C13">
+        <v>91.78</v>
+      </c>
+      <c r="D13">
+        <v>91.47</v>
+      </c>
+      <c r="E13">
+        <v>91.09</v>
+      </c>
+      <c r="F13" s="1">
+        <f t="shared" si="1"/>
+        <v>91.446666666666673</v>
+      </c>
+      <c r="H13" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="4">
+        <v>12503168</v>
+      </c>
+      <c r="C14">
+        <v>80.02</v>
+      </c>
+      <c r="D14">
+        <v>79.72</v>
+      </c>
+      <c r="E14">
+        <v>79.459999999999994</v>
+      </c>
+      <c r="F14" s="1">
+        <f t="shared" si="1"/>
+        <v>79.733333333333334</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="4">
+        <v>20099300</v>
+      </c>
+      <c r="C15">
+        <v>73.09</v>
+      </c>
+      <c r="D15">
+        <v>73.12</v>
+      </c>
+      <c r="E15">
+        <v>72.959999999999994</v>
+      </c>
+      <c r="F15" s="1">
+        <f t="shared" si="1"/>
+        <v>73.056666666666672</v>
+      </c>
+      <c r="H15" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4">
+        <v>29901464</v>
+      </c>
+      <c r="C16">
+        <v>65.760000000000005</v>
+      </c>
+      <c r="D16">
+        <v>65.849999999999994</v>
+      </c>
+      <c r="E16">
+        <v>66.239999999999995</v>
+      </c>
+      <c r="F16" s="1">
+        <f t="shared" si="1"/>
+        <v>65.95</v>
+      </c>
+      <c r="H16" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B17" s="4"/>
+      <c r="F17" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
